--- a/docs/downloads/04/tbl_raison_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_raison_alaotra_avaradrano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Accès terre</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1.1</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,14 +411,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Autre</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>1.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +434,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E4">
-        <v>13.3</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -463,14 +457,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D5">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>75.59999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6">
@@ -486,14 +480,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>7.8</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -504,19 +492,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1.1</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -532,14 +514,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Accès terre</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>1.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="9">
@@ -555,14 +537,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>41.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="10">
@@ -578,14 +560,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D10">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>47.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="11">
@@ -601,37 +583,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11">
-        <v>7.9</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1.6</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -647,14 +617,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Accès terre</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E13">
-        <v>0.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="14">
@@ -670,14 +640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Autre</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>371</v>
       </c>
       <c r="E14">
-        <v>0.2</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +663,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D15">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E15">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +686,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D16">
-        <v>371</v>
+        <v>35</v>
       </c>
       <c r="E16">
-        <v>73.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="17">
@@ -734,19 +704,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>0.2</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -757,19 +721,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D18">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="E18">
-        <v>9.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="19">
@@ -780,19 +744,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D19">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="E19">
-        <v>6.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +772,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Accès terre</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E20">
-        <v>0.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="21">
@@ -831,105 +795,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D21">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>216</v>
-      </c>
-      <c r="E22">
-        <v>58.2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>25</v>
-      </c>
-      <c r="E24">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>15</v>
-      </c>
-      <c r="E25">
         <v>4</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_raison_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_raison_alaotra_avaradrano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,7 +394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autre raison</t>
+          <t>Autre / NSP</t>
         </is>
       </c>
     </row>
@@ -411,14 +411,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E3">
-        <v>13.3</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -434,14 +434,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D4">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>75.59999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5">
@@ -452,19 +452,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E5">
-        <v>7.8</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="6">
@@ -475,105 +475,105 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Autre raison</t>
+          <t>Autre / NSP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>26</v>
-      </c>
-      <c r="E8">
-        <v>41.3</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>457</v>
       </c>
       <c r="E9">
-        <v>47.6</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E10">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Conjoncturelle (écologie, insécurité)</t>
         </is>
       </c>
     </row>
@@ -595,13 +595,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Autre raison</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>344</v>
+      </c>
+      <c r="E12">
+        <v>92.7</v>
       </c>
     </row>
     <row r="13">
@@ -612,197 +618,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D13">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>371</v>
-      </c>
-      <c r="E14">
-        <v>73.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>46</v>
-      </c>
-      <c r="E15">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>35</v>
-      </c>
-      <c r="E16">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>113</v>
-      </c>
-      <c r="E18">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>216</v>
-      </c>
-      <c r="E19">
-        <v>58.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>25</v>
-      </c>
-      <c r="E20">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>15</v>
-      </c>
-      <c r="E21">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
